--- a/data/final/06_commiters_gsynth.xlsx
+++ b/data/final/06_commiters_gsynth.xlsx
@@ -394,19 +394,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.1924979188203166</v>
+        <v>0.1924979188203143</v>
       </c>
       <c r="C2">
-        <v>0.2242056000491988</v>
+        <v>0.2501995135191102</v>
       </c>
       <c r="D2">
-        <v>0.1583796350204091</v>
+        <v>0.1674091594225774</v>
       </c>
       <c r="E2">
-        <v>-0.1179204617042838</v>
+        <v>-0.1356180043300615</v>
       </c>
       <c r="F2">
-        <v>0.5029162993449171</v>
+        <v>0.52061384197069</v>
       </c>
     </row>
     <row r="3">
@@ -416,19 +416,19 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.1550967142791811</v>
+        <v>0.155096714279181</v>
       </c>
       <c r="C3">
-        <v>0.3224312009494237</v>
+        <v>0.3263171311559518</v>
       </c>
       <c r="D3">
-        <v>0.1567466021984217</v>
+        <v>0.1580105798845979</v>
       </c>
       <c r="E3">
-        <v>-0.1521209807287521</v>
+        <v>-0.1545983314709199</v>
       </c>
       <c r="F3">
-        <v>0.4623144092871142</v>
+        <v>0.4647917600292819</v>
       </c>
     </row>
     <row r="4">
@@ -438,19 +438,19 @@
         </is>
       </c>
       <c r="B4">
-        <v>-0.2001188808375007</v>
+        <v>-0.2001188808375015</v>
       </c>
       <c r="C4">
-        <v>0.08700902394563315</v>
+        <v>0.08298256450716224</v>
       </c>
       <c r="D4">
-        <v>0.1169334903353358</v>
+        <v>0.1154329975201801</v>
       </c>
       <c r="E4">
-        <v>-0.4293043104813212</v>
+        <v>-0.4263633986045557</v>
       </c>
       <c r="F4">
-        <v>0.02906654880631981</v>
+        <v>0.02612563692955286</v>
       </c>
     </row>
     <row r="5">
@@ -460,19 +460,19 @@
         </is>
       </c>
       <c r="B5">
-        <v>-0.04927352809279798</v>
+        <v>-0.04927352809279884</v>
       </c>
       <c r="C5">
-        <v>0.6828565365319015</v>
+        <v>0.6773760707123431</v>
       </c>
       <c r="D5">
-        <v>0.1206004832165623</v>
+        <v>0.1184327790676194</v>
       </c>
       <c r="E5">
-        <v>-0.2856461317153873</v>
+        <v>-0.281397509654322</v>
       </c>
       <c r="F5">
-        <v>0.1870990755297914</v>
+        <v>0.1828504534687244</v>
       </c>
     </row>
     <row r="6">
@@ -482,19 +482,19 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.113133101517351</v>
+        <v>0.1131331015173504</v>
       </c>
       <c r="C6">
-        <v>0.2883498788523917</v>
+        <v>0.3045145851021014</v>
       </c>
       <c r="D6">
-        <v>0.1065535787341925</v>
+        <v>0.11018025562683</v>
       </c>
       <c r="E6">
-        <v>-0.09570807522551911</v>
+        <v>-0.1028162313186529</v>
       </c>
       <c r="F6">
-        <v>0.3219742782602212</v>
+        <v>0.3290824343533537</v>
       </c>
     </row>
     <row r="7">
@@ -504,19 +504,19 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.09979502111789458</v>
+        <v>0.09979502111789312</v>
       </c>
       <c r="C7">
-        <v>0.3894207262446723</v>
+        <v>0.4055233895770103</v>
       </c>
       <c r="D7">
-        <v>0.1159506102867497</v>
+        <v>0.1199751738366073</v>
       </c>
       <c r="E7">
-        <v>-0.1274639990295743</v>
+        <v>-0.1353519986407893</v>
       </c>
       <c r="F7">
-        <v>0.3270540412653634</v>
+        <v>0.3349420408765755</v>
       </c>
     </row>
     <row r="8">
@@ -526,19 +526,19 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.06577440129554701</v>
+        <v>0.06577440129554638</v>
       </c>
       <c r="C8">
-        <v>0.580243527847021</v>
+        <v>0.5898616361455777</v>
       </c>
       <c r="D8">
-        <v>0.1189348063473341</v>
+        <v>0.1220221550789384</v>
       </c>
       <c r="E8">
-        <v>-0.1673335356534736</v>
+        <v>-0.173384627975134</v>
       </c>
       <c r="F8">
-        <v>0.2988823382445676</v>
+        <v>0.3049334305662268</v>
       </c>
     </row>
     <row r="9">
@@ -548,19 +548,19 @@
         </is>
       </c>
       <c r="B9">
-        <v>-0.1198041604795425</v>
+        <v>-0.1198041604795437</v>
       </c>
       <c r="C9">
-        <v>0.3337242417497253</v>
+        <v>0.3182942723883304</v>
       </c>
       <c r="D9">
-        <v>0.1239388114539407</v>
+        <v>0.1200479484832871</v>
       </c>
       <c r="E9">
-        <v>-0.3627197672159665</v>
+        <v>-0.3550938159247062</v>
       </c>
       <c r="F9">
-        <v>0.1231114462568814</v>
+        <v>0.1154854949656188</v>
       </c>
     </row>
     <row r="10">
@@ -570,19 +570,19 @@
         </is>
       </c>
       <c r="B10">
-        <v>-0.2163699164829005</v>
+        <v>-0.2163699164829019</v>
       </c>
       <c r="C10">
-        <v>0.1059431771021431</v>
+        <v>0.1094797728702728</v>
       </c>
       <c r="D10">
-        <v>0.1338343494859761</v>
+        <v>0.1351859279086595</v>
       </c>
       <c r="E10">
-        <v>-0.4786804213697602</v>
+        <v>-0.4813294664005027</v>
       </c>
       <c r="F10">
-        <v>0.04594058840395929</v>
+        <v>0.04858963343469891</v>
       </c>
     </row>
     <row r="11">
@@ -592,19 +592,19 @@
         </is>
       </c>
       <c r="B11">
-        <v>-0.2358648450507537</v>
+        <v>-0.2358648450507554</v>
       </c>
       <c r="C11">
-        <v>0.03674369371479402</v>
+        <v>0.0462696756665133</v>
       </c>
       <c r="D11">
-        <v>0.1129296086007475</v>
+        <v>0.1183510978267873</v>
       </c>
       <c r="E11">
-        <v>-0.4572028106964234</v>
+        <v>-0.4678287343220351</v>
       </c>
       <c r="F11">
-        <v>-0.01452687940508393</v>
+        <v>-0.003900955779475745</v>
       </c>
     </row>
     <row r="12">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="B12">
-        <v>-0.09024016011492003</v>
+        <v>-0.09024016011492196</v>
       </c>
       <c r="C12">
-        <v>0.5738605399671539</v>
+        <v>0.5531895139908205</v>
       </c>
       <c r="D12">
-        <v>0.1604626060886938</v>
+        <v>0.1521788558075433</v>
       </c>
       <c r="E12">
-        <v>-0.4047410889141974</v>
+        <v>-0.3885052367062207</v>
       </c>
       <c r="F12">
-        <v>0.2242607686843573</v>
+        <v>0.2080249164763768</v>
       </c>
     </row>
     <row r="13">
@@ -636,19 +636,19 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.07881597711329438</v>
+        <v>0.07881597711329316</v>
       </c>
       <c r="C13">
-        <v>0.4602025361643038</v>
+        <v>0.4478243356787386</v>
       </c>
       <c r="D13">
-        <v>0.1067224760727057</v>
+        <v>0.1038354129167673</v>
       </c>
       <c r="E13">
-        <v>-0.1303562323301463</v>
+        <v>-0.1246976925234158</v>
       </c>
       <c r="F13">
-        <v>0.2879881865567351</v>
+        <v>0.2823296467500022</v>
       </c>
     </row>
     <row r="14">
@@ -658,19 +658,19 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.3776412554962649</v>
+        <v>0.377641255496263</v>
       </c>
       <c r="C14">
-        <v>0.001693480095076083</v>
+        <v>0.002210698014044388</v>
       </c>
       <c r="D14">
-        <v>0.1202944702541213</v>
+        <v>0.1233975873342698</v>
       </c>
       <c r="E14">
-        <v>0.1418684262588625</v>
+        <v>0.1357864285419584</v>
       </c>
       <c r="F14">
-        <v>0.6134140847336673</v>
+        <v>0.6194960824505676</v>
       </c>
     </row>
     <row r="15">
@@ -680,19 +680,19 @@
         </is>
       </c>
       <c r="B15">
-        <v>-0.1002016876471108</v>
+        <v>-0.1002016876471123</v>
       </c>
       <c r="C15">
-        <v>0.5129299277856059</v>
+        <v>0.5373622949665517</v>
       </c>
       <c r="D15">
-        <v>0.1531474763120706</v>
+        <v>0.1624523584205714</v>
       </c>
       <c r="E15">
-        <v>-0.4003652255419702</v>
+        <v>-0.4186024593550244</v>
       </c>
       <c r="F15">
-        <v>0.1999618502477486</v>
+        <v>0.2181990840607997</v>
       </c>
     </row>
     <row r="16">
@@ -702,19 +702,19 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.1206524068631584</v>
+        <v>0.1206524068631575</v>
       </c>
       <c r="C16">
-        <v>0.4052356429612265</v>
+        <v>0.418300529652293</v>
       </c>
       <c r="D16">
-        <v>0.1449614111478534</v>
+        <v>0.1490689477030392</v>
       </c>
       <c r="E16">
-        <v>-0.1634667381347372</v>
+        <v>-0.1715173618480841</v>
       </c>
       <c r="F16">
-        <v>0.404771551861054</v>
+        <v>0.4128221755743992</v>
       </c>
     </row>
     <row r="17">
@@ -724,19 +724,19 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.005879409380499968</v>
+        <v>0.005879409380499695</v>
       </c>
       <c r="C17">
-        <v>0.9596343387843298</v>
+        <v>0.9607418306915494</v>
       </c>
       <c r="D17">
-        <v>0.1161652702012543</v>
+        <v>0.1194451097179089</v>
       </c>
       <c r="E17">
-        <v>-0.2218003364683223</v>
+        <v>-0.228228703796037</v>
       </c>
       <c r="F17">
-        <v>0.2335591552293223</v>
+        <v>0.2399875225570364</v>
       </c>
     </row>
     <row r="18">
@@ -746,19 +746,19 @@
         </is>
       </c>
       <c r="B18">
-        <v>-0.01330421082708393</v>
+        <v>-0.01330421082708378</v>
       </c>
       <c r="C18">
-        <v>0.9184900768864115</v>
+        <v>0.9210013661523275</v>
       </c>
       <c r="D18">
-        <v>0.130005339887622</v>
+        <v>0.1341523152132892</v>
       </c>
       <c r="E18">
-        <v>-0.2681099948047115</v>
+        <v>-0.2762379170877952</v>
       </c>
       <c r="F18">
-        <v>0.2415015731505436</v>
+        <v>0.2496294954336277</v>
       </c>
     </row>
     <row r="19">
@@ -768,19 +768,19 @@
         </is>
       </c>
       <c r="B19">
-        <v>0.06939662920981662</v>
+        <v>0.06939662920981607</v>
       </c>
       <c r="C19">
-        <v>0.5147367397652656</v>
+        <v>0.5245038341475807</v>
       </c>
       <c r="D19">
-        <v>0.106521517933579</v>
+        <v>0.1090424838408263</v>
       </c>
       <c r="E19">
-        <v>-0.1393817095185357</v>
+        <v>-0.1443227119029943</v>
       </c>
       <c r="F19">
-        <v>0.278174967938169</v>
+        <v>0.2831159703226265</v>
       </c>
     </row>
     <row r="20">
@@ -790,19 +790,19 @@
         </is>
       </c>
       <c r="B20">
-        <v>0.03802591898508594</v>
+        <v>0.03802591898508514</v>
       </c>
       <c r="C20">
-        <v>0.6987922843544652</v>
+        <v>0.7205451932576299</v>
       </c>
       <c r="D20">
-        <v>0.09827056268739834</v>
+        <v>0.106297745376535</v>
       </c>
       <c r="E20">
-        <v>-0.1545808446227004</v>
+        <v>-0.1703138335907324</v>
       </c>
       <c r="F20">
-        <v>0.2306326825928723</v>
+        <v>0.2463656715609027</v>
       </c>
     </row>
     <row r="21">
@@ -812,19 +812,19 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.04445525294919214</v>
+        <v>0.04445525294919046</v>
       </c>
       <c r="C21">
-        <v>0.7689495024176649</v>
+        <v>0.7648808335706785</v>
       </c>
       <c r="D21">
-        <v>0.1513374075001282</v>
+        <v>0.1486411963233065</v>
       </c>
       <c r="E21">
-        <v>-0.2521606152647209</v>
+        <v>-0.2468761384634376</v>
       </c>
       <c r="F21">
-        <v>0.3410711211631051</v>
+        <v>0.3357866443618185</v>
       </c>
     </row>
     <row r="22">
@@ -834,19 +834,19 @@
         </is>
       </c>
       <c r="B22">
-        <v>-0.027494458501598</v>
+        <v>-0.02749445850159905</v>
       </c>
       <c r="C22">
-        <v>0.85597305869398</v>
+        <v>0.8544267909398382</v>
       </c>
       <c r="D22">
-        <v>0.1514824138539653</v>
+        <v>0.1498554952484104</v>
       </c>
       <c r="E22">
-        <v>-0.3243945339465612</v>
+        <v>-0.3212058320738966</v>
       </c>
       <c r="F22">
-        <v>0.2694056169433652</v>
+        <v>0.2662169150706985</v>
       </c>
     </row>
     <row r="23">
@@ -856,19 +856,19 @@
         </is>
       </c>
       <c r="B23">
-        <v>-0.1783386937105887</v>
+        <v>-0.1783386937105899</v>
       </c>
       <c r="C23">
-        <v>0.2084969648117165</v>
+        <v>0.230552676731631</v>
       </c>
       <c r="D23">
-        <v>0.1417964517807784</v>
+        <v>0.148747417909668</v>
       </c>
       <c r="E23">
-        <v>-0.4562546323364848</v>
+        <v>-0.4698782756068672</v>
       </c>
       <c r="F23">
-        <v>0.09957724491530731</v>
+        <v>0.1132008881856875</v>
       </c>
     </row>
     <row r="24">
@@ -878,19 +878,19 @@
         </is>
       </c>
       <c r="B24">
-        <v>-0.03190841380230961</v>
+        <v>-0.03190841380231164</v>
       </c>
       <c r="C24">
-        <v>0.7801091325152119</v>
+        <v>0.7993105170515931</v>
       </c>
       <c r="D24">
-        <v>0.114294639252208</v>
+        <v>0.1255053234241134</v>
       </c>
       <c r="E24">
-        <v>-0.2559217903626352</v>
+        <v>-0.2778943275816251</v>
       </c>
       <c r="F24">
-        <v>0.1921049627580159</v>
+        <v>0.2140774999770018</v>
       </c>
     </row>
     <row r="25">
@@ -900,19 +900,19 @@
         </is>
       </c>
       <c r="B25">
-        <v>-0.01191354010875937</v>
+        <v>-0.01191354010876076</v>
       </c>
       <c r="C25">
-        <v>0.9352002022378669</v>
+        <v>0.9406074063583585</v>
       </c>
       <c r="D25">
-        <v>0.1465308203019533</v>
+        <v>0.1598994390762362</v>
       </c>
       <c r="E25">
-        <v>-0.2991086705256983</v>
+        <v>-0.3253106818463402</v>
       </c>
       <c r="F25">
-        <v>0.2752815903081795</v>
+        <v>0.3014836016288187</v>
       </c>
     </row>
     <row r="26">
@@ -922,19 +922,19 @@
         </is>
       </c>
       <c r="B26">
-        <v>-0.05180523250257993</v>
+        <v>-0.0518052325025813</v>
       </c>
       <c r="C26">
-        <v>0.6703696716902039</v>
+        <v>0.6738939734368568</v>
       </c>
       <c r="D26">
-        <v>0.1217111788642209</v>
+        <v>0.1231084263037902</v>
       </c>
       <c r="E26">
-        <v>-0.2903547595923655</v>
+        <v>-0.2930933142514136</v>
       </c>
       <c r="F26">
-        <v>0.1867442945872056</v>
+        <v>0.1894828492462509</v>
       </c>
     </row>
     <row r="27">
@@ -944,19 +944,19 @@
         </is>
       </c>
       <c r="B27">
-        <v>0.2907777667392659</v>
+        <v>0.290777766739265</v>
       </c>
       <c r="C27">
-        <v>0.04129501560845994</v>
+        <v>0.0319026659993753</v>
       </c>
       <c r="D27">
-        <v>0.1424993083047265</v>
+        <v>0.1355210504715386</v>
       </c>
       <c r="E27">
-        <v>0.0114842546401327</v>
+        <v>0.02516138866801454</v>
       </c>
       <c r="F27">
-        <v>0.570071278838399</v>
+        <v>0.5563941448105155</v>
       </c>
     </row>
     <row r="28">
@@ -966,19 +966,19 @@
         </is>
       </c>
       <c r="B28">
-        <v>0.0407754774717096</v>
+        <v>0.0407754774717079</v>
       </c>
       <c r="C28">
-        <v>0.7589087167754942</v>
+        <v>0.7644033618645829</v>
       </c>
       <c r="D28">
-        <v>0.1328562960974712</v>
+        <v>0.1360527434451432</v>
       </c>
       <c r="E28">
-        <v>-0.2196180779987231</v>
+        <v>-0.2258829996786406</v>
       </c>
       <c r="F28">
-        <v>0.3011690329421423</v>
+        <v>0.3074339546220564</v>
       </c>
     </row>
     <row r="29">
@@ -988,19 +988,19 @@
         </is>
       </c>
       <c r="B29">
-        <v>0.2060350922576441</v>
+        <v>0.2060350922576429</v>
       </c>
       <c r="C29">
-        <v>0.0964849532332539</v>
+        <v>0.1032799718445219</v>
       </c>
       <c r="D29">
-        <v>0.1239578161519554</v>
+        <v>0.1264673709162971</v>
       </c>
       <c r="E29">
-        <v>-0.03691776300242586</v>
+        <v>-0.04183639995776767</v>
       </c>
       <c r="F29">
-        <v>0.4489879475177141</v>
+        <v>0.4539065844730535</v>
       </c>
     </row>
     <row r="30">
@@ -1010,19 +1010,19 @@
         </is>
       </c>
       <c r="B30">
-        <v>-0.0625049918166438</v>
+        <v>-0.06250499181664464</v>
       </c>
       <c r="C30">
-        <v>0.6273175701288021</v>
+        <v>0.636383654457922</v>
       </c>
       <c r="D30">
-        <v>0.1287419975067256</v>
+        <v>0.1322126469037735</v>
       </c>
       <c r="E30">
-        <v>-0.3148346702275714</v>
+        <v>-0.3216370180487518</v>
       </c>
       <c r="F30">
-        <v>0.1898246865942838</v>
+        <v>0.1966270344154625</v>
       </c>
     </row>
     <row r="31">
@@ -1032,19 +1032,19 @@
         </is>
       </c>
       <c r="B31">
-        <v>-0.02451975198388599</v>
+        <v>-0.02451975198388529</v>
       </c>
       <c r="C31">
-        <v>0.8326481629801352</v>
+        <v>0.851960730559389</v>
       </c>
       <c r="D31">
-        <v>0.1160388331105579</v>
+        <v>0.1313905883135058</v>
       </c>
       <c r="E31">
-        <v>-0.2519516856886334</v>
+        <v>-0.2820405729858859</v>
       </c>
       <c r="F31">
-        <v>0.2029121817208614</v>
+        <v>0.2330010690181153</v>
       </c>
     </row>
     <row r="32">
@@ -1054,19 +1054,19 @@
         </is>
       </c>
       <c r="B32">
-        <v>-0.2421145350684569</v>
+        <v>-0.242114535068456</v>
       </c>
       <c r="C32">
-        <v>0.04622504351899459</v>
+        <v>0.04509420701292854</v>
       </c>
       <c r="D32">
-        <v>0.1214621885903217</v>
+        <v>0.1208292243623939</v>
       </c>
       <c r="E32">
-        <v>-0.4801760501888992</v>
+        <v>-0.4789354630986578</v>
       </c>
       <c r="F32">
-        <v>-0.004053019948014547</v>
+        <v>-0.005293607038254322</v>
       </c>
     </row>
     <row r="33">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="B33">
-        <v>-0.1576632387888665</v>
+        <v>-0.1576632387888656</v>
       </c>
       <c r="C33">
-        <v>0.199684488017978</v>
+        <v>0.207860643821375</v>
       </c>
       <c r="D33">
-        <v>0.1229389975901381</v>
+        <v>0.1251822172945753</v>
       </c>
       <c r="E33">
-        <v>-0.3986192463609937</v>
+        <v>-0.4030158761911003</v>
       </c>
       <c r="F33">
-        <v>0.08329276878326067</v>
+        <v>0.08768939861336905</v>
       </c>
     </row>
     <row r="34">
@@ -1098,19 +1098,19 @@
         </is>
       </c>
       <c r="B34">
-        <v>-0.1121373101105583</v>
+        <v>-0.1121373101105582</v>
       </c>
       <c r="C34">
-        <v>0.3112733433044534</v>
+        <v>0.3230551141892761</v>
       </c>
       <c r="D34">
-        <v>0.1107470157370249</v>
+        <v>0.1134764260296706</v>
       </c>
       <c r="E34">
-        <v>-0.3291974723504176</v>
+        <v>-0.334547018223036</v>
       </c>
       <c r="F34">
-        <v>0.104922852129301</v>
+        <v>0.1102723980019197</v>
       </c>
     </row>
     <row r="35">
@@ -1120,19 +1120,19 @@
         </is>
       </c>
       <c r="B35">
-        <v>0.04676135360483535</v>
+        <v>0.04676135360483583</v>
       </c>
       <c r="C35">
-        <v>0.7142930195100403</v>
+        <v>0.7049887964997508</v>
       </c>
       <c r="D35">
-        <v>0.1277295606921454</v>
+        <v>0.1235129369133522</v>
       </c>
       <c r="E35">
-        <v>-0.2035839851128924</v>
+        <v>-0.1953195543701022</v>
       </c>
       <c r="F35">
-        <v>0.2971066923225631</v>
+        <v>0.2888422615797739</v>
       </c>
     </row>
     <row r="36">
@@ -1142,19 +1142,19 @@
         </is>
       </c>
       <c r="B36">
-        <v>0.08196252081952109</v>
+        <v>0.08196252081952135</v>
       </c>
       <c r="C36">
-        <v>0.4765341594889125</v>
+        <v>0.4866564196130485</v>
       </c>
       <c r="D36">
-        <v>0.1151340177571201</v>
+        <v>0.1178237561603491</v>
       </c>
       <c r="E36">
-        <v>-0.1436960073798293</v>
+        <v>-0.1489677977779922</v>
       </c>
       <c r="F36">
-        <v>0.3076210490188715</v>
+        <v>0.3128928394170348</v>
       </c>
     </row>
     <row r="37">
@@ -1164,19 +1164,19 @@
         </is>
       </c>
       <c r="B37">
-        <v>0.1024267744739038</v>
+        <v>0.102426774473904</v>
       </c>
       <c r="C37">
-        <v>0.4636125577041272</v>
+        <v>0.4898052699995228</v>
       </c>
       <c r="D37">
-        <v>0.139753310779921</v>
+        <v>0.1483116410215388</v>
       </c>
       <c r="E37">
-        <v>-0.1714846813749744</v>
+        <v>-0.1882587004163451</v>
       </c>
       <c r="F37">
-        <v>0.3763382303227821</v>
+        <v>0.3931122493641532</v>
       </c>
     </row>
     <row r="38">
@@ -1186,19 +1186,19 @@
         </is>
       </c>
       <c r="B38">
-        <v>-0.09102052036164526</v>
+        <v>-0.09102052036164399</v>
       </c>
       <c r="C38">
-        <v>0.506171460903081</v>
+        <v>0.4936572121808855</v>
       </c>
       <c r="D38">
-        <v>0.1369118988304688</v>
+        <v>0.1329730323824169</v>
       </c>
       <c r="E38">
-        <v>-0.3593629111243555</v>
+        <v>-0.3516428747462593</v>
       </c>
       <c r="F38">
-        <v>0.177321870401065</v>
+        <v>0.1696018340229713</v>
       </c>
     </row>
     <row r="39">
@@ -1208,19 +1208,19 @@
         </is>
       </c>
       <c r="B39">
-        <v>-0.02372996073727379</v>
+        <v>-0.02372996073727326</v>
       </c>
       <c r="C39">
-        <v>0.8481837077894265</v>
+        <v>0.8470584024663823</v>
       </c>
       <c r="D39">
-        <v>0.1239574150412483</v>
+        <v>0.1230341015882178</v>
       </c>
       <c r="E39">
-        <v>-0.2666820298348039</v>
+        <v>-0.2648723687204222</v>
       </c>
       <c r="F39">
-        <v>0.2192221083602563</v>
+        <v>0.2174124472458757</v>
       </c>
     </row>
     <row r="40">
@@ -1230,19 +1230,19 @@
         </is>
       </c>
       <c r="B40">
-        <v>-0.03524983203880865</v>
+        <v>-0.03524983203880855</v>
       </c>
       <c r="C40">
-        <v>0.7963386620093598</v>
+        <v>0.8009599591268857</v>
       </c>
       <c r="D40">
-        <v>0.136580443651064</v>
+        <v>0.1398220652977482</v>
       </c>
       <c r="E40">
-        <v>-0.3029425825873964</v>
+        <v>-0.3092960442664027</v>
       </c>
       <c r="F40">
-        <v>0.2324429185097791</v>
+        <v>0.2387963801887856</v>
       </c>
     </row>
     <row r="41">
@@ -1252,19 +1252,19 @@
         </is>
       </c>
       <c r="B41">
-        <v>0.1528934268285021</v>
+        <v>0.1528934268285026</v>
       </c>
       <c r="C41">
-        <v>0.2474645748071331</v>
+        <v>0.23491847373404</v>
       </c>
       <c r="D41">
-        <v>0.1322001779080931</v>
+        <v>0.1287215620416916</v>
       </c>
       <c r="E41">
-        <v>-0.106214160621148</v>
+        <v>-0.099396198806951</v>
       </c>
       <c r="F41">
-        <v>0.4120010142781522</v>
+        <v>0.4051830524639562</v>
       </c>
     </row>
     <row r="42">
@@ -1274,19 +1274,19 @@
         </is>
       </c>
       <c r="B42">
-        <v>-0.1754279053104234</v>
+        <v>-0.1754279053104257</v>
       </c>
       <c r="C42">
-        <v>0.2813189878128073</v>
+        <v>0.2788669736762259</v>
       </c>
       <c r="D42">
-        <v>0.1628311155528539</v>
+        <v>0.162003022873792</v>
       </c>
       <c r="E42">
-        <v>-0.4945710273564967</v>
+        <v>-0.4929479955296765</v>
       </c>
       <c r="F42">
-        <v>0.1437152167356499</v>
+        <v>0.1420921849088252</v>
       </c>
     </row>
     <row r="43">
@@ -1296,19 +1296,19 @@
         </is>
       </c>
       <c r="B43">
-        <v>-0.07691181408034006</v>
+        <v>-0.07691181408034095</v>
       </c>
       <c r="C43">
-        <v>0.5927918316263781</v>
+        <v>0.6133270907577104</v>
       </c>
       <c r="D43">
-        <v>0.1438155889697477</v>
+        <v>0.1522011704029284</v>
       </c>
       <c r="E43">
-        <v>-0.3587851888764614</v>
+        <v>-0.3752206264749243</v>
       </c>
       <c r="F43">
-        <v>0.2049615607157813</v>
+        <v>0.2213969983142423</v>
       </c>
     </row>
     <row r="44">
@@ -1318,19 +1318,19 @@
         </is>
       </c>
       <c r="B44">
-        <v>0.1881718120940603</v>
+        <v>0.1881718120940599</v>
       </c>
       <c r="C44">
-        <v>0.2225088047271704</v>
+        <v>0.2214522534870969</v>
       </c>
       <c r="D44">
-        <v>0.1542538412282477</v>
+        <v>0.153901668592528</v>
       </c>
       <c r="E44">
-        <v>-0.1141601611902649</v>
+        <v>-0.1134699155079141</v>
       </c>
       <c r="F44">
-        <v>0.4905037853783855</v>
+        <v>0.4898135396960339</v>
       </c>
     </row>
     <row r="45">
@@ -1340,19 +1340,19 @@
         </is>
       </c>
       <c r="B45">
-        <v>-0.05375331340347009</v>
+        <v>-0.05375331340347098</v>
       </c>
       <c r="C45">
-        <v>0.692261392269822</v>
+        <v>0.6919487327590041</v>
       </c>
       <c r="D45">
-        <v>0.1358133809965207</v>
+        <v>0.1356681033434582</v>
       </c>
       <c r="E45">
-        <v>-0.3199426487752672</v>
+        <v>-0.3196579098075072</v>
       </c>
       <c r="F45">
-        <v>0.212436021968327</v>
+        <v>0.2121512830005652</v>
       </c>
     </row>
     <row r="46">
@@ -1362,19 +1362,19 @@
         </is>
       </c>
       <c r="B46">
-        <v>0.1445711616684433</v>
+        <v>0.1445711616684435</v>
       </c>
       <c r="C46">
-        <v>0.221983409243419</v>
+        <v>0.2363914870314499</v>
       </c>
       <c r="D46">
-        <v>0.1183776207539321</v>
+        <v>0.1220984007513291</v>
       </c>
       <c r="E46">
-        <v>-0.08744471158480477</v>
+        <v>-0.09473730637409966</v>
       </c>
       <c r="F46">
-        <v>0.3765870349216913</v>
+        <v>0.3838796297109867</v>
       </c>
     </row>
     <row r="47">
@@ -1384,19 +1384,19 @@
         </is>
       </c>
       <c r="B47">
-        <v>-0.04683274321745425</v>
+        <v>-0.04683274321745292</v>
       </c>
       <c r="C47">
-        <v>0.7449812515388998</v>
+        <v>0.7438125506112041</v>
       </c>
       <c r="D47">
-        <v>0.143983775734889</v>
+        <v>0.143303216460612</v>
       </c>
       <c r="E47">
-        <v>-0.3290357580159288</v>
+        <v>-0.3277018863489998</v>
       </c>
       <c r="F47">
-        <v>0.2353702715810203</v>
+        <v>0.234036399914094</v>
       </c>
     </row>
     <row r="48">
@@ -1406,19 +1406,19 @@
         </is>
       </c>
       <c r="B48">
-        <v>-0.005639670345894988</v>
+        <v>-0.005639670345892836</v>
       </c>
       <c r="C48">
-        <v>0.9587298894245666</v>
+        <v>0.9593999257513175</v>
       </c>
       <c r="D48">
-        <v>0.1089844048055704</v>
+        <v>0.1107846033763708</v>
       </c>
       <c r="E48">
-        <v>-0.219245178641347</v>
+        <v>-0.222773503005134</v>
       </c>
       <c r="F48">
-        <v>0.207965837949557</v>
+        <v>0.2114941623133484</v>
       </c>
     </row>
     <row r="49">
@@ -1428,19 +1428,19 @@
         </is>
       </c>
       <c r="B49">
-        <v>-0.1007262063264144</v>
+        <v>-0.1007262063264122</v>
       </c>
       <c r="C49">
-        <v>0.5152887475708654</v>
+        <v>0.5183517671395514</v>
       </c>
       <c r="D49">
-        <v>0.1548145929574156</v>
+        <v>0.1559499113720542</v>
       </c>
       <c r="E49">
-        <v>-0.404157232804177</v>
+        <v>-0.4063824160078517</v>
       </c>
       <c r="F49">
-        <v>0.2027048201513484</v>
+        <v>0.2049300033550273</v>
       </c>
     </row>
     <row r="50">
@@ -1450,19 +1450,19 @@
         </is>
       </c>
       <c r="B50">
-        <v>-0.2774647232760945</v>
+        <v>-0.2774647232760907</v>
       </c>
       <c r="C50">
-        <v>0.06410161204169862</v>
+        <v>0.06762911936715765</v>
       </c>
       <c r="D50">
-        <v>0.1498616523292161</v>
+        <v>0.1518299669151386</v>
       </c>
       <c r="E50">
-        <v>-0.5711881645050212</v>
+        <v>-0.5750459902036703</v>
       </c>
       <c r="F50">
-        <v>0.01625871795283212</v>
+        <v>0.02011654365148885</v>
       </c>
     </row>
     <row r="51">
@@ -1472,19 +1472,19 @@
         </is>
       </c>
       <c r="B51">
-        <v>-0.03433223662796419</v>
+        <v>-0.03433223662795887</v>
       </c>
       <c r="C51">
-        <v>0.7693760812306352</v>
+        <v>0.7621157508354444</v>
       </c>
       <c r="D51">
-        <v>0.1170984924835647</v>
+        <v>0.1134186582263239</v>
       </c>
       <c r="E51">
-        <v>-0.2638410645396851</v>
+        <v>-0.2566287219264112</v>
       </c>
       <c r="F51">
-        <v>0.1951765912837568</v>
+        <v>0.1879642486704934</v>
       </c>
     </row>
     <row r="52">
@@ -1494,19 +1494,19 @@
         </is>
       </c>
       <c r="B52">
-        <v>0.08924714983479709</v>
+        <v>0.08924714983480361</v>
       </c>
       <c r="C52">
-        <v>0.5298698770716368</v>
+        <v>0.5180822723663203</v>
       </c>
       <c r="D52">
-        <v>0.1420669971438449</v>
+        <v>0.1380884254698796</v>
       </c>
       <c r="E52">
-        <v>-0.1891990479588936</v>
+        <v>-0.1814011907680038</v>
       </c>
       <c r="F52">
-        <v>0.3676933476284878</v>
+        <v>0.359895490437611</v>
       </c>
     </row>
     <row r="53">
@@ -1516,19 +1516,19 @@
         </is>
       </c>
       <c r="B53">
-        <v>0.1165738582620596</v>
+        <v>0.1165738582620656</v>
       </c>
       <c r="C53">
-        <v>0.3850878357735761</v>
+        <v>0.4219838314266247</v>
       </c>
       <c r="D53">
-        <v>0.1342150881566758</v>
+        <v>0.1451757697781039</v>
       </c>
       <c r="E53">
-        <v>-0.1464828807068933</v>
+        <v>-0.1679654219308965</v>
       </c>
       <c r="F53">
-        <v>0.3796305972310126</v>
+        <v>0.4011131384550276</v>
       </c>
     </row>
     <row r="54">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="B54">
-        <v>0.1037622975992788</v>
+        <v>0.1037622975992875</v>
       </c>
       <c r="C54">
-        <v>0.578281519518703</v>
+        <v>0.5639035637166643</v>
       </c>
       <c r="D54">
-        <v>0.1866575389718073</v>
+        <v>0.1798141138788281</v>
       </c>
       <c r="E54">
-        <v>-0.2620797562283449</v>
+        <v>-0.2486668895151995</v>
       </c>
       <c r="F54">
-        <v>0.4696043514269026</v>
+        <v>0.4561914847137745</v>
       </c>
     </row>
     <row r="55">
@@ -1560,19 +1560,19 @@
         </is>
       </c>
       <c r="B55">
-        <v>0.3490181900811962</v>
+        <v>0.3490181900812044</v>
       </c>
       <c r="C55">
-        <v>0.09018915034936104</v>
+        <v>0.1125473555429912</v>
       </c>
       <c r="D55">
-        <v>0.2059832555824414</v>
+        <v>0.2199444829754928</v>
       </c>
       <c r="E55">
-        <v>-0.05470157227869787</v>
+        <v>-0.08206507514904443</v>
       </c>
       <c r="F55">
-        <v>0.7527379524410902</v>
+        <v>0.7801014553114531</v>
       </c>
     </row>
     <row r="56">
@@ -1582,19 +1582,19 @@
         </is>
       </c>
       <c r="B56">
-        <v>0.369886887900458</v>
+        <v>0.3698868879004668</v>
       </c>
       <c r="C56">
-        <v>0.09786945783278922</v>
+        <v>0.0913055974526269</v>
       </c>
       <c r="D56">
-        <v>0.2234599644070741</v>
+        <v>0.2190558594235165</v>
       </c>
       <c r="E56">
-        <v>-0.06808659432400949</v>
+        <v>-0.0594547071720945</v>
       </c>
       <c r="F56">
-        <v>0.8078603701249254</v>
+        <v>0.7992284829730281</v>
       </c>
     </row>
     <row r="57">
@@ -1604,19 +1604,19 @@
         </is>
       </c>
       <c r="B57">
-        <v>0.2869933209287328</v>
+        <v>0.2869933209287414</v>
       </c>
       <c r="C57">
-        <v>0.1706423460295639</v>
+        <v>0.1838948149931947</v>
       </c>
       <c r="D57">
-        <v>0.2094623508778549</v>
+        <v>0.2159698898878795</v>
       </c>
       <c r="E57">
-        <v>-0.1235453429089544</v>
+        <v>-0.1362998849965836</v>
       </c>
       <c r="F57">
-        <v>0.69753198476642</v>
+        <v>0.7102865268540663</v>
       </c>
     </row>
     <row r="58">
@@ -1626,19 +1626,19 @@
         </is>
       </c>
       <c r="B58">
-        <v>0.394773254822111</v>
+        <v>0.3947732548221199</v>
       </c>
       <c r="C58">
-        <v>0.1188704289226179</v>
+        <v>0.1220451166240906</v>
       </c>
       <c r="D58">
-        <v>0.2531356591357599</v>
+        <v>0.2553107335702336</v>
       </c>
       <c r="E58">
-        <v>-0.1013635202867858</v>
+        <v>-0.1056265878420392</v>
       </c>
       <c r="F58">
-        <v>0.8909100299310078</v>
+        <v>0.8951730974862789</v>
       </c>
     </row>
     <row r="59">
@@ -1648,19 +1648,19 @@
         </is>
       </c>
       <c r="B59">
-        <v>0.2912857760610889</v>
+        <v>0.2912857760610985</v>
       </c>
       <c r="C59">
-        <v>0.308909657189421</v>
+        <v>0.3101371744379837</v>
       </c>
       <c r="D59">
-        <v>0.2862724113697459</v>
+        <v>0.2869996538813926</v>
       </c>
       <c r="E59">
-        <v>-0.2697978399910476</v>
+        <v>-0.2712232091218919</v>
       </c>
       <c r="F59">
-        <v>0.8523693921132253</v>
+        <v>0.8537947612440889</v>
       </c>
     </row>
     <row r="60">
@@ -1670,19 +1670,19 @@
         </is>
       </c>
       <c r="B60">
-        <v>0.3930373298413241</v>
+        <v>0.3930373298413333</v>
       </c>
       <c r="C60">
-        <v>0.1814207593721537</v>
+        <v>0.1613521700217078</v>
       </c>
       <c r="D60">
-        <v>0.2941030411408528</v>
+        <v>0.2806330380500001</v>
       </c>
       <c r="E60">
-        <v>-0.183394038538449</v>
+        <v>-0.1569933176087253</v>
       </c>
       <c r="F60">
-        <v>0.9694686982210973</v>
+        <v>0.9430679772913919</v>
       </c>
     </row>
     <row r="61">
@@ -1692,19 +1692,19 @@
         </is>
       </c>
       <c r="B61">
-        <v>0.5619761530601644</v>
+        <v>0.5619761530601736</v>
       </c>
       <c r="C61">
-        <v>0.065214036258604</v>
+        <v>0.07166288560429757</v>
       </c>
       <c r="D61">
-        <v>0.3047943367602455</v>
+        <v>0.311991653865818</v>
       </c>
       <c r="E61">
-        <v>-0.0354097696816893</v>
+        <v>-0.04951625199391618</v>
       </c>
       <c r="F61">
-        <v>1.159362075802018</v>
+        <v>1.173468558114263</v>
       </c>
     </row>
     <row r="62">
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B62">
-        <v>0.5766621209488861</v>
+        <v>0.5766621209488966</v>
       </c>
       <c r="C62">
-        <v>0.04777449098985964</v>
+        <v>0.05433385724366535</v>
       </c>
       <c r="D62">
-        <v>0.2913363599556855</v>
+        <v>0.2996946766224285</v>
       </c>
       <c r="E62">
-        <v>0.00565334804874551</v>
+        <v>-0.01072865158944114</v>
       </c>
       <c r="F62">
-        <v>1.147670893849027</v>
+        <v>1.164052893487234</v>
       </c>
     </row>
     <row r="63">
@@ -1736,19 +1736,19 @@
         </is>
       </c>
       <c r="B63">
-        <v>0.6701625305858069</v>
+        <v>0.6701625305858171</v>
       </c>
       <c r="C63">
-        <v>0.03397388553393377</v>
+        <v>0.03524023947448662</v>
       </c>
       <c r="D63">
-        <v>0.3160575257215769</v>
+        <v>0.3182782369795387</v>
       </c>
       <c r="E63">
-        <v>0.05070116312867456</v>
+        <v>0.04634864904301705</v>
       </c>
       <c r="F63">
-        <v>1.289623898042939</v>
+        <v>1.293976412128617</v>
       </c>
     </row>
     <row r="64">
@@ -1758,19 +1758,19 @@
         </is>
       </c>
       <c r="B64">
-        <v>0.7269637997998259</v>
+        <v>0.7269637997998362</v>
       </c>
       <c r="C64">
-        <v>0.01272222710012705</v>
+        <v>0.0189380560077117</v>
       </c>
       <c r="D64">
-        <v>0.2917832225703242</v>
+        <v>0.3097749673706019</v>
       </c>
       <c r="E64">
-        <v>0.1550791922689562</v>
+        <v>0.1198160204413863</v>
       </c>
       <c r="F64">
-        <v>1.298848407330696</v>
+        <v>1.334111579158286</v>
       </c>
     </row>
     <row r="65">
@@ -1780,19 +1780,19 @@
         </is>
       </c>
       <c r="B65">
-        <v>1.297298459138552</v>
+        <v>1.29729845913856</v>
       </c>
       <c r="C65">
-        <v>1.562758481998827E-05</v>
+        <v>2.14382289298598E-05</v>
       </c>
       <c r="D65">
-        <v>0.3003248021594029</v>
+        <v>0.3052926805521017</v>
       </c>
       <c r="E65">
-        <v>0.7086726632420056</v>
+        <v>0.6989358005127493</v>
       </c>
       <c r="F65">
-        <v>1.885924255035099</v>
+        <v>1.895661117764371</v>
       </c>
     </row>
     <row r="66">
@@ -1802,19 +1802,19 @@
         </is>
       </c>
       <c r="B66">
-        <v>1.626578812213872</v>
+        <v>1.626578812213874</v>
       </c>
       <c r="C66">
-        <v>7.712121518133053E-05</v>
+        <v>5.346481653512036E-05</v>
       </c>
       <c r="D66">
-        <v>0.4114614453539244</v>
+        <v>0.4026244708962936</v>
       </c>
       <c r="E66">
-        <v>0.8201291982933853</v>
+        <v>0.8374493499626435</v>
       </c>
       <c r="F66">
-        <v>2.43302842613436</v>
+        <v>2.415708274465104</v>
       </c>
     </row>
   </sheetData>
@@ -1866,19 +1866,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.5165046476528589</v>
+        <v>0.5165046476528682</v>
       </c>
       <c r="C2">
-        <v>0.02444921611096418</v>
+        <v>0.02611706918259493</v>
       </c>
       <c r="D2">
-        <v>0.2295580564160858</v>
+        <v>0.2321925868631614</v>
       </c>
       <c r="E2">
-        <v>0.06657912471631688</v>
+        <v>0.06141553992388399</v>
       </c>
       <c r="F2">
-        <v>0.9664301705894008</v>
+        <v>0.9715937553818523</v>
       </c>
     </row>
   </sheetData>
